--- a/data/trans_bre/P16A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,19</t>
+          <t>-2,08; 10,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 15,87</t>
+          <t>1,99; 15,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 19,3</t>
+          <t>4,27; 19,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 22,71</t>
+          <t>6,41; 22,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 102,79</t>
+          <t>-12,98; 96,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 122,46</t>
+          <t>9,83; 114,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,59; 110,12</t>
+          <t>15,67; 110,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,29; 96,66</t>
+          <t>17,86; 90,13</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 17,42</t>
+          <t>8,26; 17,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 19,78</t>
+          <t>8,06; 19,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 18,36</t>
+          <t>7,83; 18,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 23,15</t>
+          <t>11,34; 23,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,03; 236,22</t>
+          <t>71,65; 222,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,19; 107,7</t>
+          <t>35,55; 102,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,54; 122,09</t>
+          <t>40,35; 129,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,13; 118,59</t>
+          <t>41,36; 117,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 25,02</t>
+          <t>11,83; 23,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 17,1</t>
+          <t>2,43; 16,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 19,82</t>
+          <t>6,73; 20,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 20,11</t>
+          <t>6,71; 19,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,77; 304,03</t>
+          <t>88,5; 280,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 91,51</t>
+          <t>9,69; 89,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,56; 118,7</t>
+          <t>29,35; 122,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,52; 79,64</t>
+          <t>20,75; 80,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,95</t>
+          <t>1,68; 12,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,83; 28,34</t>
+          <t>14,55; 27,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 25,2</t>
+          <t>9,99; 24,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 14,9</t>
+          <t>-11,79; 15,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 108,46</t>
+          <t>9,65; 105,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,63; 176,96</t>
+          <t>63,59; 174,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 103,91</t>
+          <t>29,9; 99,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 55,07</t>
+          <t>-32,06; 56,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 18,92</t>
+          <t>2,79; 18,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,16; 35,6</t>
+          <t>19,05; 36,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 22,85</t>
+          <t>8,53; 23,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 23,54</t>
+          <t>9,39; 22,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 175,68</t>
+          <t>12,88; 163,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,78; 275,11</t>
+          <t>88,32; 285,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,6; 225,39</t>
+          <t>47,23; 221,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,85; 121,58</t>
+          <t>34,49; 123,73</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 17,83</t>
+          <t>4,82; 17,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,76; 25,35</t>
+          <t>10,71; 26,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 17,17</t>
+          <t>3,23; 17,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 20,9</t>
+          <t>6,75; 20,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,55; 158,82</t>
+          <t>28,1; 166,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,33; 156,8</t>
+          <t>45,19; 162,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,01; 149,0</t>
+          <t>11,78; 143,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,82; 83,02</t>
+          <t>20,49; 79,47</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 10,66</t>
+          <t>2,58; 11,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,74; 19,88</t>
+          <t>10,8; 20,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 11,19</t>
+          <t>2,63; 11,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 50,56</t>
+          <t>12,23; 51,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,12; 86,87</t>
+          <t>15,53; 90,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,68; 135,79</t>
+          <t>55,6; 141,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,95; 86,38</t>
+          <t>14,94; 88,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,83; 224,58</t>
+          <t>43,21; 222,17</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,41; 13,86</t>
+          <t>4,82; 13,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,79</t>
+          <t>10,63; 19,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,36</t>
+          <t>8,68; 17,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,85; 27,5</t>
+          <t>15,9; 28,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,3; 87,04</t>
+          <t>24,38; 87,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,41; 153,98</t>
+          <t>65,29; 155,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,69; 98,32</t>
+          <t>38,64; 97,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>109,5; 535,5</t>
+          <t>112,07; 549,99</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,95</t>
+          <t>8,02; 11,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,91</t>
+          <t>13,61; 17,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,26</t>
+          <t>10,29; 14,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,55; 31,22</t>
+          <t>14,13; 30,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54,56; 92,27</t>
+          <t>54,04; 91,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,06; 106,99</t>
+          <t>72,17; 104,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,19; 80,58</t>
+          <t>51,84; 80,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>60,43; 160,11</t>
+          <t>58,09; 154,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>13,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 10,4</t>
+          <t>-1,55; 11,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 15,72</t>
+          <t>2,01; 16,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 19,72</t>
+          <t>3,75; 19,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 22,27</t>
+          <t>5,67; 19,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 96,52</t>
+          <t>-10,81; 99,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 114,43</t>
+          <t>10,14; 128,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,67; 110,52</t>
+          <t>14,62; 107,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 90,13</t>
+          <t>16,34; 74,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,61</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 17,07</t>
+          <t>8,42; 17,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 19,16</t>
+          <t>8,45; 19,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 18,45</t>
+          <t>7,46; 18,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 23,12</t>
+          <t>11,31; 22,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,65; 222,12</t>
+          <t>71,95; 232,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,55; 102,98</t>
+          <t>34,66; 107,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,35; 129,14</t>
+          <t>37,78; 124,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,36; 117,6</t>
+          <t>40,79; 111,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,47</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 23,63</t>
+          <t>11,73; 23,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 16,65</t>
+          <t>3,63; 17,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 20,52</t>
+          <t>5,85; 19,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 19,66</t>
+          <t>7,14; 19,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,5; 280,18</t>
+          <t>88,01; 287,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 89,46</t>
+          <t>12,64; 91,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,35; 122,26</t>
+          <t>23,44; 117,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,75; 80,34</t>
+          <t>22,22; 79,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>14,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 12,91</t>
+          <t>2,06; 13,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 27,89</t>
+          <t>13,95; 27,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 24,74</t>
+          <t>10,01; 24,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 15,82</t>
+          <t>5,77; 21,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 105,52</t>
+          <t>11,19; 105,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,59; 174,44</t>
+          <t>61,4; 170,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 99,09</t>
+          <t>32,24; 98,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 56,11</t>
+          <t>15,27; 87,92</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,25</t>
+          <t>16,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 18,32</t>
+          <t>3,05; 18,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 36,1</t>
+          <t>18,93; 36,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 23,71</t>
+          <t>7,31; 23,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 22,95</t>
+          <t>8,86; 22,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 163,07</t>
+          <t>15,41; 172,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,32; 285,87</t>
+          <t>90,75; 285,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,23; 221,97</t>
+          <t>38,13; 226,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,49; 123,73</t>
+          <t>33,85; 124,27</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,75</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 17,51</t>
+          <t>4,95; 17,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 26,09</t>
+          <t>10,73; 25,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 17,62</t>
+          <t>3,31; 17,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 20,39</t>
+          <t>6,66; 20,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,1; 166,31</t>
+          <t>29,58; 165,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,19; 162,82</t>
+          <t>47,34; 161,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,78; 143,76</t>
+          <t>15,49; 148,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,49; 79,47</t>
+          <t>21,14; 84,26</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,64</t>
+          <t>14,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>107,66%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,04</t>
+          <t>2,54; 11,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 20,29</t>
+          <t>10,62; 20,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,27</t>
+          <t>2,75; 11,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,23; 51,82</t>
+          <t>9,13; 19,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,53; 90,05</t>
+          <t>15,49; 93,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,6; 141,14</t>
+          <t>56,64; 140,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,94; 88,32</t>
+          <t>15,56; 88,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,21; 222,17</t>
+          <t>31,13; 81,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,98</t>
+          <t>17,03</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>206,72%</t>
+          <t>128,43%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,58</t>
+          <t>4,81; 13,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,01</t>
+          <t>10,38; 19,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,68; 17,42</t>
+          <t>8,71; 17,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,9; 28,55</t>
+          <t>13,14; 20,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,38; 87,32</t>
+          <t>23,43; 85,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,29; 155,34</t>
+          <t>64,59; 157,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,64; 97,9</t>
+          <t>38,35; 99,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>112,07; 549,99</t>
+          <t>86,1; 182,94</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,84</t>
+          <t>7,95; 11,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,61; 17,67</t>
+          <t>13,39; 17,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,47</t>
+          <t>10,18; 14,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,13; 30,31</t>
+          <t>13,22; 17,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54,04; 91,16</t>
+          <t>54,29; 88,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,17; 104,2</t>
+          <t>71,9; 104,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,84; 80,0</t>
+          <t>51,61; 81,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>58,09; 154,29</t>
+          <t>52,97; 76,03</t>
         </is>
       </c>
     </row>
